--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.7-threat-intelligence/WKBK/90_workbooks/ISMS-IMP-A.5.7.3_Integration_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.7-threat-intelligence/WKBK/90_workbooks/ISMS-IMP-A.5.7.3_Integration_20260208.xlsx
@@ -3709,7 +3709,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-02-08 11:49:15</t>
+          <t>2026-02-08 12:25:42</t>
         </is>
       </c>
     </row>
